--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130751762</v>
+        <v>130751852</v>
       </c>
       <c r="B7" t="n">
         <v>79211</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490779</v>
+        <v>490760</v>
       </c>
       <c r="R7" t="n">
-        <v>6763206</v>
+        <v>6763211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130751852</v>
+        <v>130751762</v>
       </c>
       <c r="B8" t="n">
         <v>79211</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490760</v>
+        <v>490779</v>
       </c>
       <c r="R8" t="n">
-        <v>6763211</v>
+        <v>6763206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130752874</v>
+        <v>130752842</v>
       </c>
       <c r="B17" t="n">
         <v>79211</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490655</v>
+        <v>490660</v>
       </c>
       <c r="R17" t="n">
-        <v>6763493</v>
+        <v>6763462</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130752842</v>
+        <v>130752874</v>
       </c>
       <c r="B18" t="n">
         <v>79211</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490660</v>
+        <v>490655</v>
       </c>
       <c r="R18" t="n">
-        <v>6763462</v>
+        <v>6763493</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2736,6 +2736,1990 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130789515</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57851</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>490723</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6763501</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130789503</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490685</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6763486</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130789501</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490713</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6763507</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130789509</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490693</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6763417</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130789462</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57854</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490705</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6763439</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ring hack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130789504</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>490686</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6763480</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130789505</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>490697</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6763451</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130789510</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>490692</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6763414</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130789514</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>490800</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6763195</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130789512</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>490686</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6763382</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130789502</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>490712</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6763506</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130789507</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>490706</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6763438</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130789461</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57854</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>490783</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6763515</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130789466</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>490710</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6763505</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130789506</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>490698</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6763446</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130789513</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>490777</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6763210</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130789508</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>490700</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6763430</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130789511</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>490679</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6763384</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130752197</v>
+        <v>130789515</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490715</v>
+        <v>490723</v>
       </c>
       <c r="R2" t="n">
-        <v>6763290</v>
+        <v>6763501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +778,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130752899</v>
+        <v>130789503</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490652</v>
+        <v>490685</v>
       </c>
       <c r="R3" t="n">
-        <v>6763503</v>
+        <v>6763486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,28 +879,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130751615</v>
+        <v>130752197</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +909,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490779</v>
+        <v>490715</v>
       </c>
       <c r="R4" t="n">
-        <v>6763206</v>
+        <v>6763290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,17 +998,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130752192</v>
+        <v>130752899</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,39 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490715</v>
+        <v>490652</v>
       </c>
       <c r="R5" t="n">
-        <v>6763290</v>
+        <v>6763503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,17 +1105,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130752527</v>
+        <v>130751615</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1123,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490673</v>
+        <v>490779</v>
       </c>
       <c r="R6" t="n">
-        <v>6763435</v>
+        <v>6763206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,17 +1217,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130751852</v>
+        <v>130789501</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,14 +1255,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490760</v>
+        <v>490713</v>
       </c>
       <c r="R7" t="n">
-        <v>6763211</v>
+        <v>6763507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,28 +1313,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130751762</v>
+        <v>130752192</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,34 +1343,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490779</v>
+        <v>490715</v>
       </c>
       <c r="R8" t="n">
-        <v>6763206</v>
+        <v>6763290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,17 +1437,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130753551</v>
+        <v>130789509</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490770</v>
+        <v>490693</v>
       </c>
       <c r="R9" t="n">
-        <v>6763512</v>
+        <v>6763417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,28 +1533,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130752453</v>
+        <v>130752527</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490682</v>
+        <v>490673</v>
       </c>
       <c r="R10" t="n">
-        <v>6763392</v>
+        <v>6763435</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,17 +1652,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130752039</v>
+        <v>130789462</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,34 +1670,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490739</v>
+        <v>490705</v>
       </c>
       <c r="R11" t="n">
-        <v>6763241</v>
+        <v>6763439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1747,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ring hack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1767,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130753344</v>
+        <v>130751852</v>
       </c>
       <c r="B12" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,39 +1790,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490761</v>
+        <v>490760</v>
       </c>
       <c r="R12" t="n">
-        <v>6763503</v>
+        <v>6763211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,11 +1862,6 @@
           <t>11:43</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3 Bilder</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1865,17 +1879,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130752740</v>
+        <v>130789504</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490682</v>
+        <v>490686</v>
       </c>
       <c r="R13" t="n">
-        <v>6763461</v>
+        <v>6763480</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1961,28 +1975,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130752001</v>
+        <v>130751762</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490746</v>
+        <v>490779</v>
       </c>
       <c r="R14" t="n">
-        <v>6763219</v>
+        <v>6763206</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,17 +2094,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130752569</v>
+        <v>130789505</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490661</v>
+        <v>490697</v>
       </c>
       <c r="R15" t="n">
-        <v>6763445</v>
+        <v>6763451</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2181,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,28 +2190,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130751938</v>
+        <v>130789510</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,14 +2240,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490749</v>
+        <v>490692</v>
       </c>
       <c r="R16" t="n">
-        <v>6763201</v>
+        <v>6763414</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2279,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2289,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,28 +2298,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130752842</v>
+        <v>130753551</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490660</v>
+        <v>490770</v>
       </c>
       <c r="R17" t="n">
-        <v>6763462</v>
+        <v>6763512</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,17 +2417,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130752874</v>
+        <v>130789514</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490655</v>
+        <v>490800</v>
       </c>
       <c r="R18" t="n">
-        <v>6763493</v>
+        <v>6763195</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2494,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2504,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2496,28 +2513,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130753055</v>
+        <v>130752453</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,10 +2567,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490658</v>
+        <v>490682</v>
       </c>
       <c r="R19" t="n">
-        <v>6763532</v>
+        <v>6763392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,17 +2632,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130753455</v>
+        <v>130789512</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,39 +2650,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490770</v>
+        <v>490686</v>
       </c>
       <c r="R20" t="n">
-        <v>6763512</v>
+        <v>6763382</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2709,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2706,12 +2719,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bild 4 till 6</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,28 +2728,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130789515</v>
+        <v>130752039</v>
       </c>
       <c r="B21" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,42 +2758,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490723</v>
+        <v>490739</v>
       </c>
       <c r="R21" t="n">
-        <v>6763501</v>
+        <v>6763241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2817,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2827,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2841,22 +2842,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130789503</v>
+        <v>130789502</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490685</v>
+        <v>490712</v>
       </c>
       <c r="R22" t="n">
-        <v>6763486</v>
+        <v>6763506</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2923,7 +2924,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2933,7 +2934,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130789501</v>
+        <v>130753344</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,34 +2973,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490713</v>
+        <v>490761</v>
       </c>
       <c r="R23" t="n">
-        <v>6763507</v>
+        <v>6763503</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3041,7 +3047,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3 Bilder</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3050,29 +3061,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130789509</v>
+        <v>130752740</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3104,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490693</v>
+        <v>490682</v>
       </c>
       <c r="R24" t="n">
-        <v>6763417</v>
+        <v>6763461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,7 +3149,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3159,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3158,29 +3168,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130789462</v>
+        <v>130752001</v>
       </c>
       <c r="B25" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,42 +3197,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490705</v>
+        <v>490746</v>
       </c>
       <c r="R25" t="n">
-        <v>6763439</v>
+        <v>6763219</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,7 +3256,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3265,12 +3266,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ring hack på tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3285,22 +3281,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130789504</v>
+        <v>130789507</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3332,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490686</v>
+        <v>490706</v>
       </c>
       <c r="R26" t="n">
-        <v>6763480</v>
+        <v>6763438</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3363,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3377,7 +3373,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3405,10 +3401,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130789505</v>
+        <v>130752569</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490697</v>
+        <v>490661</v>
       </c>
       <c r="R27" t="n">
-        <v>6763451</v>
+        <v>6763445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,7 +3471,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3485,7 +3481,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3494,29 +3490,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130789510</v>
+        <v>130751938</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,14 +3539,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490692</v>
+        <v>490749</v>
       </c>
       <c r="R28" t="n">
-        <v>6763414</v>
+        <v>6763201</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3593,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3602,29 +3597,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130789514</v>
+        <v>130789461</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3632,34 +3626,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490800</v>
+        <v>490783</v>
       </c>
       <c r="R29" t="n">
-        <v>6763195</v>
+        <v>6763515</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3693,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3703,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3710,7 +3717,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3729,45 +3735,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130789512</v>
+        <v>130789466</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490686</v>
+        <v>490710</v>
       </c>
       <c r="R30" t="n">
-        <v>6763382</v>
+        <v>6763505</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3799,7 +3814,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3809,7 +3824,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3837,10 +3852,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130789502</v>
+        <v>130789506</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3872,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490712</v>
+        <v>490698</v>
       </c>
       <c r="R31" t="n">
-        <v>6763506</v>
+        <v>6763446</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3917,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3945,10 +3960,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130789507</v>
+        <v>130752874</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3980,10 +3995,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490706</v>
+        <v>490655</v>
       </c>
       <c r="R32" t="n">
-        <v>6763438</v>
+        <v>6763493</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4015,7 +4030,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4025,7 +4040,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4034,29 +4049,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130789461</v>
+        <v>130752842</v>
       </c>
       <c r="B33" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,42 +4078,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490783</v>
+        <v>490660</v>
       </c>
       <c r="R33" t="n">
-        <v>6763515</v>
+        <v>6763462</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4137,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4141,12 +4147,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4161,66 +4162,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130789466</v>
+        <v>130789513</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490710</v>
+        <v>490777</v>
       </c>
       <c r="R34" t="n">
-        <v>6763505</v>
+        <v>6763210</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4252,7 +4244,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4262,7 +4254,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4290,10 +4282,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130789506</v>
+        <v>130753055</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4325,10 +4317,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490698</v>
+        <v>490658</v>
       </c>
       <c r="R35" t="n">
-        <v>6763446</v>
+        <v>6763532</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4360,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4370,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4379,29 +4371,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130789513</v>
+        <v>130789508</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4433,10 +4424,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490777</v>
+        <v>490700</v>
       </c>
       <c r="R36" t="n">
-        <v>6763210</v>
+        <v>6763430</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4468,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4478,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4506,10 +4497,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130789508</v>
+        <v>130753455</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4517,34 +4508,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490700</v>
+        <v>490770</v>
       </c>
       <c r="R37" t="n">
-        <v>6763430</v>
+        <v>6763512</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,7 +4572,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4586,7 +4582,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bild 4 till 6</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4595,19 +4596,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4617,7 +4617,7 @@
         <v>130789511</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130789515</v>
+        <v>130789503</v>
       </c>
       <c r="B2" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490723</v>
+        <v>490685</v>
       </c>
       <c r="R2" t="n">
-        <v>6763501</v>
+        <v>6763486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130789503</v>
+        <v>130789515</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +794,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490685</v>
+        <v>490723</v>
       </c>
       <c r="R3" t="n">
-        <v>6763486</v>
+        <v>6763501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +880,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +901,7 @@
         <v>130752197</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>130752899</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>130751615</v>
       </c>
       <c r="B6" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>130789501</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130752192</v>
+        <v>130789509</v>
       </c>
       <c r="B8" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,39 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490715</v>
+        <v>490693</v>
       </c>
       <c r="R8" t="n">
-        <v>6763290</v>
+        <v>6763417</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,28 +1421,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130789509</v>
+        <v>130752192</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,34 +1451,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490693</v>
+        <v>490715</v>
       </c>
       <c r="R9" t="n">
-        <v>6763417</v>
+        <v>6763290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1515,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1525,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,19 +1534,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
         <v>130752527</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>130789462</v>
       </c>
       <c r="B11" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>130751852</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>130789504</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>130751762</v>
       </c>
       <c r="B14" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>130789505</v>
       </c>
       <c r="B15" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>130789510</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>130753551</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>130789514</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>130752453</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>130789512</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130752039</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>130789502</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>130753344</v>
       </c>
       <c r="B23" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>130752740</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>130752001</v>
       </c>
       <c r="B25" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>130789507</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>130752569</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>130751938</v>
       </c>
       <c r="B28" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>130789461</v>
       </c>
       <c r="B29" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,54 +3735,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130789466</v>
+        <v>130789506</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490710</v>
+        <v>490698</v>
       </c>
       <c r="R30" t="n">
-        <v>6763505</v>
+        <v>6763446</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3814,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3824,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3852,45 +3843,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130789506</v>
+        <v>130789466</v>
       </c>
       <c r="B31" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490698</v>
+        <v>490710</v>
       </c>
       <c r="R31" t="n">
-        <v>6763446</v>
+        <v>6763505</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,7 +3963,7 @@
         <v>130752874</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>130752842</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>130789513</v>
       </c>
       <c r="B34" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>130753055</v>
       </c>
       <c r="B35" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>130789508</v>
       </c>
       <c r="B36" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>130753455</v>
       </c>
       <c r="B37" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>130789511</v>
       </c>
       <c r="B38" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4719,6 +4719,1589 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130807229</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Truppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>490993</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6763224</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 bilder på tall. Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130807313</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57863</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Truppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>490990</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6763195</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2 bilder på tall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130812290</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57860</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Truppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>490970</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6763268</v>
+      </c>
+      <c r="S41" t="n">
+        <v>50</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130815610</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>490831</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6763410</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter. 2 bilder på tall och gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130807544</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Truppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>491106</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6763223</v>
+      </c>
+      <c r="S43" t="n">
+        <v>50</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 bilder på gran vid basväg samt tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130815695</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57863</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>490815</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6763446</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3 bilder på tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130807362</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Truppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>490990</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6763195</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130815959</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57863</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>490727</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6763422</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>3 bilder på tall</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130815712</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>490815</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6763446</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130815999</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>490722</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6763404</v>
+      </c>
+      <c r="S48" t="n">
+        <v>50</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter. 2 bilder tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130814260</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57863</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Truppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>490982</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6763304</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>4 bilder på tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130811340</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Truppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>491007</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6763275</v>
+      </c>
+      <c r="S50" t="n">
+        <v>50</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>1 bild på gran. Måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130815884</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57863</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>490768</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6763431</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>3 bilder på tall, ett tydligt ringhack</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130813058</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Truppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>490951</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6763295</v>
+      </c>
+      <c r="S52" t="n">
+        <v>50</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>3 bilder på tall och gran</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130789503</v>
+        <v>130789515</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490685</v>
+        <v>490723</v>
       </c>
       <c r="R2" t="n">
-        <v>6763486</v>
+        <v>6763501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130789515</v>
+        <v>130789503</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490723</v>
+        <v>490685</v>
       </c>
       <c r="R3" t="n">
-        <v>6763501</v>
+        <v>6763486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130752197</v>
+        <v>130752899</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,14 +929,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490715</v>
+        <v>490652</v>
       </c>
       <c r="R4" t="n">
-        <v>6763290</v>
+        <v>6763503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130752899</v>
+        <v>130752197</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,14 +1036,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490652</v>
+        <v>490715</v>
       </c>
       <c r="R5" t="n">
-        <v>6763503</v>
+        <v>6763290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
         <v>130751615</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130789501</v>
+        <v>130789509</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490713</v>
+        <v>490693</v>
       </c>
       <c r="R7" t="n">
-        <v>6763507</v>
+        <v>6763417</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130789509</v>
+        <v>130789501</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490693</v>
+        <v>490713</v>
       </c>
       <c r="R8" t="n">
-        <v>6763417</v>
+        <v>6763507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,7 +1443,7 @@
         <v>130752192</v>
       </c>
       <c r="B9" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>130752527</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>130789462</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130751852</v>
+        <v>130751762</v>
       </c>
       <c r="B12" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490760</v>
+        <v>490779</v>
       </c>
       <c r="R12" t="n">
-        <v>6763211</v>
+        <v>6763206</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130789504</v>
+        <v>130751852</v>
       </c>
       <c r="B13" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,14 +1917,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490686</v>
+        <v>490760</v>
       </c>
       <c r="R13" t="n">
-        <v>6763480</v>
+        <v>6763211</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,29 +1975,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130751762</v>
+        <v>130789505</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,14 +2024,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490779</v>
+        <v>490697</v>
       </c>
       <c r="R14" t="n">
-        <v>6763206</v>
+        <v>6763451</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2074,7 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2083,28 +2082,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130789505</v>
+        <v>130789504</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490697</v>
+        <v>490686</v>
       </c>
       <c r="R15" t="n">
-        <v>6763451</v>
+        <v>6763480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,7 +2212,7 @@
         <v>130789510</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>130753551</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130789514</v>
+        <v>130752453</v>
       </c>
       <c r="B18" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490800</v>
+        <v>490682</v>
       </c>
       <c r="R18" t="n">
-        <v>6763195</v>
+        <v>6763392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,29 +2513,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130752453</v>
+        <v>130789512</v>
       </c>
       <c r="B19" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490682</v>
+        <v>490686</v>
       </c>
       <c r="R19" t="n">
-        <v>6763392</v>
+        <v>6763382</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,7 +2601,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2612,7 +2611,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,28 +2620,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130789512</v>
+        <v>130789514</v>
       </c>
       <c r="B20" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490686</v>
+        <v>490800</v>
       </c>
       <c r="R20" t="n">
-        <v>6763382</v>
+        <v>6763195</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2750,7 +2750,7 @@
         <v>130752039</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>130789502</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>130753344</v>
       </c>
       <c r="B23" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130752740</v>
+        <v>130752001</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,14 +3110,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490682</v>
+        <v>490746</v>
       </c>
       <c r="R24" t="n">
-        <v>6763461</v>
+        <v>6763219</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130752001</v>
+        <v>130752740</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,14 +3217,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490746</v>
+        <v>490682</v>
       </c>
       <c r="R25" t="n">
-        <v>6763219</v>
+        <v>6763461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3296,7 +3296,7 @@
         <v>130789507</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>130752569</v>
       </c>
       <c r="B27" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>130751938</v>
       </c>
       <c r="B28" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>130789461</v>
       </c>
       <c r="B29" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3735,45 +3735,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130789506</v>
+        <v>130789466</v>
       </c>
       <c r="B30" t="n">
-        <v>79220</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490698</v>
+        <v>490710</v>
       </c>
       <c r="R30" t="n">
-        <v>6763446</v>
+        <v>6763505</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3814,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3824,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,54 +3852,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130789466</v>
+        <v>130789506</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490710</v>
+        <v>490698</v>
       </c>
       <c r="R31" t="n">
-        <v>6763505</v>
+        <v>6763446</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,7 +3963,7 @@
         <v>130752874</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>130752842</v>
       </c>
       <c r="B33" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130789513</v>
+        <v>130753455</v>
       </c>
       <c r="B34" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4185,34 +4185,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490777</v>
+        <v>490770</v>
       </c>
       <c r="R34" t="n">
-        <v>6763210</v>
+        <v>6763512</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4244,7 +4249,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4254,7 +4259,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bild 4 till 6</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4263,29 +4273,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130753055</v>
+        <v>130789508</v>
       </c>
       <c r="B35" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4317,10 +4326,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490658</v>
+        <v>490700</v>
       </c>
       <c r="R35" t="n">
-        <v>6763532</v>
+        <v>6763430</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4361,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4371,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4371,28 +4380,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130789508</v>
+        <v>130789513</v>
       </c>
       <c r="B36" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4424,10 +4434,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490700</v>
+        <v>490777</v>
       </c>
       <c r="R36" t="n">
-        <v>6763430</v>
+        <v>6763210</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,7 +4469,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4479,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4497,10 +4507,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130753455</v>
+        <v>130753055</v>
       </c>
       <c r="B37" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4508,39 +4518,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490770</v>
+        <v>490658</v>
       </c>
       <c r="R37" t="n">
-        <v>6763512</v>
+        <v>6763532</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4583,11 +4588,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Bild 4 till 6</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,7 +4617,7 @@
         <v>130789511</v>
       </c>
       <c r="B38" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>130807229</v>
       </c>
       <c r="B39" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>130807313</v>
       </c>
       <c r="B40" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>130812290</v>
       </c>
       <c r="B41" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>130815610</v>
       </c>
       <c r="B42" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>130807544</v>
       </c>
       <c r="B43" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>130815695</v>
       </c>
       <c r="B44" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5404,10 +5404,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130807362</v>
+        <v>130815959</v>
       </c>
       <c r="B45" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5415,34 +5415,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490990</v>
+        <v>490727</v>
       </c>
       <c r="R45" t="n">
-        <v>6763195</v>
+        <v>6763422</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5485,6 +5490,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3 bilder på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5511,10 +5521,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130815959</v>
+        <v>130807362</v>
       </c>
       <c r="B46" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5522,39 +5532,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490727</v>
+        <v>490990</v>
       </c>
       <c r="R46" t="n">
-        <v>6763422</v>
+        <v>6763195</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5597,11 +5602,6 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>3 bilder på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5631,7 +5631,7 @@
         <v>130815712</v>
       </c>
       <c r="B47" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>130815999</v>
       </c>
       <c r="B48" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>130814260</v>
       </c>
       <c r="B49" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>130811340</v>
       </c>
       <c r="B50" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>130815884</v>
       </c>
       <c r="B51" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>130813058</v>
       </c>
       <c r="B52" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130789515</v>
+        <v>130789503</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490723</v>
+        <v>490685</v>
       </c>
       <c r="R2" t="n">
-        <v>6763501</v>
+        <v>6763486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130789503</v>
+        <v>130789515</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +794,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490685</v>
+        <v>490723</v>
       </c>
       <c r="R3" t="n">
-        <v>6763486</v>
+        <v>6763501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +880,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -3735,54 +3735,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130789466</v>
+        <v>130789506</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490710</v>
+        <v>490698</v>
       </c>
       <c r="R30" t="n">
-        <v>6763505</v>
+        <v>6763446</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3814,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3824,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3852,45 +3843,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130789506</v>
+        <v>130789466</v>
       </c>
       <c r="B31" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490698</v>
+        <v>490710</v>
       </c>
       <c r="R31" t="n">
-        <v>6763446</v>
+        <v>6763505</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4174,10 +4174,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130753455</v>
+        <v>130789508</v>
       </c>
       <c r="B34" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4185,39 +4185,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490770</v>
+        <v>490700</v>
       </c>
       <c r="R34" t="n">
-        <v>6763512</v>
+        <v>6763430</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4249,7 +4244,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4259,12 +4254,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Bild 4 till 6</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4273,25 +4263,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130789508</v>
+        <v>130789513</v>
       </c>
       <c r="B35" t="n">
         <v>79221</v>
@@ -4326,10 +4317,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490700</v>
+        <v>490777</v>
       </c>
       <c r="R35" t="n">
-        <v>6763430</v>
+        <v>6763210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4361,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4371,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4399,7 +4390,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130789513</v>
+        <v>130753055</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4434,10 +4425,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490777</v>
+        <v>490658</v>
       </c>
       <c r="R36" t="n">
-        <v>6763210</v>
+        <v>6763532</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4469,7 +4460,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4479,7 +4470,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,29 +4479,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130753055</v>
+        <v>130753455</v>
       </c>
       <c r="B37" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4518,34 +4508,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490658</v>
+        <v>490770</v>
       </c>
       <c r="R37" t="n">
-        <v>6763532</v>
+        <v>6763512</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4588,6 +4583,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bild 4 till 6</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130752899</v>
+        <v>130752197</v>
       </c>
       <c r="B4" t="n">
         <v>79221</v>
@@ -929,14 +929,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490652</v>
+        <v>490715</v>
       </c>
       <c r="R4" t="n">
-        <v>6763503</v>
+        <v>6763290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130752197</v>
+        <v>130752899</v>
       </c>
       <c r="B5" t="n">
         <v>79221</v>
@@ -1036,14 +1036,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490715</v>
+        <v>490652</v>
       </c>
       <c r="R5" t="n">
-        <v>6763290</v>
+        <v>6763503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130789509</v>
+        <v>130789501</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490693</v>
+        <v>490713</v>
       </c>
       <c r="R7" t="n">
-        <v>6763417</v>
+        <v>6763507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130789501</v>
+        <v>130789509</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490713</v>
+        <v>490693</v>
       </c>
       <c r="R8" t="n">
-        <v>6763507</v>
+        <v>6763417</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1779,7 +1779,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130751762</v>
+        <v>130751852</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490779</v>
+        <v>490760</v>
       </c>
       <c r="R12" t="n">
-        <v>6763206</v>
+        <v>6763211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130751852</v>
+        <v>130789504</v>
       </c>
       <c r="B13" t="n">
         <v>79221</v>
@@ -1917,14 +1917,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490760</v>
+        <v>490686</v>
       </c>
       <c r="R13" t="n">
-        <v>6763211</v>
+        <v>6763480</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,25 +1975,26 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130789505</v>
+        <v>130751762</v>
       </c>
       <c r="B14" t="n">
         <v>79221</v>
@@ -2024,14 +2025,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490697</v>
+        <v>490779</v>
       </c>
       <c r="R14" t="n">
-        <v>6763451</v>
+        <v>6763206</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2064,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2074,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,26 +2083,25 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130789504</v>
+        <v>130789505</v>
       </c>
       <c r="B15" t="n">
         <v>79221</v>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490686</v>
+        <v>490697</v>
       </c>
       <c r="R15" t="n">
-        <v>6763480</v>
+        <v>6763451</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2424,7 +2424,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130752453</v>
+        <v>130789514</v>
       </c>
       <c r="B18" t="n">
         <v>79221</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490682</v>
+        <v>490800</v>
       </c>
       <c r="R18" t="n">
-        <v>6763392</v>
+        <v>6763195</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,25 +2513,26 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130789512</v>
+        <v>130752453</v>
       </c>
       <c r="B19" t="n">
         <v>79221</v>
@@ -2566,10 +2567,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490686</v>
+        <v>490682</v>
       </c>
       <c r="R19" t="n">
-        <v>6763382</v>
+        <v>6763392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2602,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2611,7 +2612,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2620,26 +2621,25 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130789514</v>
+        <v>130789512</v>
       </c>
       <c r="B20" t="n">
         <v>79221</v>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490800</v>
+        <v>490686</v>
       </c>
       <c r="R20" t="n">
-        <v>6763195</v>
+        <v>6763382</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3079,7 +3079,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130752001</v>
+        <v>130752740</v>
       </c>
       <c r="B24" t="n">
         <v>79221</v>
@@ -3110,14 +3110,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490746</v>
+        <v>490682</v>
       </c>
       <c r="R24" t="n">
-        <v>6763219</v>
+        <v>6763461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130752740</v>
+        <v>130752001</v>
       </c>
       <c r="B25" t="n">
         <v>79221</v>
@@ -3217,14 +3217,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490682</v>
+        <v>490746</v>
       </c>
       <c r="R25" t="n">
-        <v>6763461</v>
+        <v>6763219</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130789508</v>
+        <v>130789513</v>
       </c>
       <c r="B34" t="n">
         <v>79221</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490700</v>
+        <v>490777</v>
       </c>
       <c r="R34" t="n">
-        <v>6763430</v>
+        <v>6763210</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130789513</v>
+        <v>130753055</v>
       </c>
       <c r="B35" t="n">
         <v>79221</v>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490777</v>
+        <v>490658</v>
       </c>
       <c r="R35" t="n">
-        <v>6763210</v>
+        <v>6763532</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4371,26 +4371,25 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130753055</v>
+        <v>130789508</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4425,10 +4424,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490658</v>
+        <v>490700</v>
       </c>
       <c r="R36" t="n">
-        <v>6763532</v>
+        <v>6763430</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4460,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4470,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4479,18 +4478,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5063,10 +5063,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130815610</v>
+        <v>130815695</v>
       </c>
       <c r="B42" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5074,37 +5074,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490831</v>
+        <v>490815</v>
       </c>
       <c r="R42" t="n">
-        <v>6763410</v>
+        <v>6763446</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5148,7 +5153,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Måttligt i en radie av ca 50 meter. 2 bilder på tall och gran</t>
+          <t>3 bilder på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5175,7 +5180,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130807544</v>
+        <v>130815610</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5206,14 +5211,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491106</v>
+        <v>490831</v>
       </c>
       <c r="R43" t="n">
-        <v>6763223</v>
+        <v>6763410</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5260,7 +5265,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>2 bilder på gran vid basväg samt tall</t>
+          <t>Måttligt i en radie av ca 50 meter. 2 bilder på tall och gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5287,10 +5292,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130815695</v>
+        <v>130807544</v>
       </c>
       <c r="B44" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5298,42 +5303,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490815</v>
+        <v>491106</v>
       </c>
       <c r="R44" t="n">
-        <v>6763446</v>
+        <v>6763223</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>3 bilder på tall</t>
+          <t>2 bilder på gran vid basväg samt tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130815999</v>
+        <v>130814260</v>
       </c>
       <c r="B48" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5746,37 +5746,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490722</v>
+        <v>490982</v>
       </c>
       <c r="R48" t="n">
-        <v>6763404</v>
+        <v>6763304</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5820,7 +5825,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Måttligt i en radie av ca 50 meter. 2 bilder tall</t>
+          <t>4 bilder på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5847,10 +5852,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130814260</v>
+        <v>130815999</v>
       </c>
       <c r="B49" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5858,42 +5863,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490982</v>
+        <v>490722</v>
       </c>
       <c r="R49" t="n">
-        <v>6763304</v>
+        <v>6763404</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>4 bilder på tall</t>
+          <t>Måttligt i en radie av ca 50 meter. 2 bilder tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130789503</v>
+        <v>130789515</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490685</v>
+        <v>490723</v>
       </c>
       <c r="R2" t="n">
-        <v>6763486</v>
+        <v>6763501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130789515</v>
+        <v>130789503</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490723</v>
+        <v>490685</v>
       </c>
       <c r="R3" t="n">
-        <v>6763501</v>
+        <v>6763486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130814260</v>
+        <v>130815999</v>
       </c>
       <c r="B48" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5746,42 +5746,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490982</v>
+        <v>490722</v>
       </c>
       <c r="R48" t="n">
-        <v>6763304</v>
+        <v>6763404</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5825,7 +5820,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4 bilder på tall</t>
+          <t>Måttligt i en radie av ca 50 meter. 2 bilder tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5852,10 +5847,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130815999</v>
+        <v>130814260</v>
       </c>
       <c r="B49" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5863,37 +5858,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490722</v>
+        <v>490982</v>
       </c>
       <c r="R49" t="n">
-        <v>6763404</v>
+        <v>6763304</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Måttligt i en radie av ca 50 meter. 2 bilder tall</t>
+          <t>4 bilder på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130789515</v>
+        <v>130789503</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490723</v>
+        <v>490685</v>
       </c>
       <c r="R2" t="n">
-        <v>6763501</v>
+        <v>6763486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130789503</v>
+        <v>130789515</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +794,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490685</v>
+        <v>490723</v>
       </c>
       <c r="R3" t="n">
-        <v>6763486</v>
+        <v>6763501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +880,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130789502</v>
+        <v>130753344</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,34 +2865,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490712</v>
+        <v>490761</v>
       </c>
       <c r="R22" t="n">
-        <v>6763506</v>
+        <v>6763503</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2924,7 +2929,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2934,7 +2939,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3 Bilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2943,29 +2953,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130753344</v>
+        <v>130789502</v>
       </c>
       <c r="B23" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,39 +2982,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490761</v>
+        <v>490712</v>
       </c>
       <c r="R23" t="n">
-        <v>6763503</v>
+        <v>6763506</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,12 +3051,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3 Bilder</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3061,18 +3060,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130789513</v>
+        <v>130753455</v>
       </c>
       <c r="B34" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4185,34 +4185,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490777</v>
+        <v>490770</v>
       </c>
       <c r="R34" t="n">
-        <v>6763210</v>
+        <v>6763512</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4244,7 +4249,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4254,7 +4259,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bild 4 till 6</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4263,26 +4273,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130753055</v>
+        <v>130789513</v>
       </c>
       <c r="B35" t="n">
         <v>79221</v>
@@ -4317,10 +4326,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490658</v>
+        <v>490777</v>
       </c>
       <c r="R35" t="n">
-        <v>6763532</v>
+        <v>6763210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4361,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4371,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4371,25 +4380,26 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130789508</v>
+        <v>130753055</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4424,10 +4434,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490700</v>
+        <v>490658</v>
       </c>
       <c r="R36" t="n">
-        <v>6763430</v>
+        <v>6763532</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,7 +4469,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4479,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4478,29 +4488,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130753455</v>
+        <v>130789508</v>
       </c>
       <c r="B37" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4508,39 +4517,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490770</v>
+        <v>490700</v>
       </c>
       <c r="R37" t="n">
-        <v>6763512</v>
+        <v>6763430</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4582,12 +4586,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Bild 4 till 6</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4596,18 +4595,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5063,10 +5063,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130815695</v>
+        <v>130815610</v>
       </c>
       <c r="B42" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5074,42 +5074,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490815</v>
+        <v>490831</v>
       </c>
       <c r="R42" t="n">
-        <v>6763446</v>
+        <v>6763410</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5153,7 +5148,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3 bilder på tall</t>
+          <t>Måttligt i en radie av ca 50 meter. 2 bilder på tall och gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5180,7 +5175,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130815610</v>
+        <v>130807544</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5211,14 +5206,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490831</v>
+        <v>491106</v>
       </c>
       <c r="R43" t="n">
-        <v>6763410</v>
+        <v>6763223</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5265,7 +5260,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Måttligt i en radie av ca 50 meter. 2 bilder på tall och gran</t>
+          <t>2 bilder på gran vid basväg samt tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5292,10 +5287,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130807544</v>
+        <v>130815695</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5303,37 +5298,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491106</v>
+        <v>490815</v>
       </c>
       <c r="R44" t="n">
-        <v>6763223</v>
+        <v>6763446</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2 bilder på gran vid basväg samt tall</t>
+          <t>3 bilder på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130815999</v>
+        <v>130814260</v>
       </c>
       <c r="B48" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5746,37 +5746,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490722</v>
+        <v>490982</v>
       </c>
       <c r="R48" t="n">
-        <v>6763404</v>
+        <v>6763304</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5820,7 +5825,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Måttligt i en radie av ca 50 meter. 2 bilder tall</t>
+          <t>4 bilder på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5847,10 +5852,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130814260</v>
+        <v>130815999</v>
       </c>
       <c r="B49" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5858,42 +5863,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490982</v>
+        <v>490722</v>
       </c>
       <c r="R49" t="n">
-        <v>6763304</v>
+        <v>6763404</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>4 bilder på tall</t>
+          <t>Måttligt i en radie av ca 50 meter. 2 bilder tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130789503</v>
+        <v>130751762</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490685</v>
+        <v>490779</v>
       </c>
       <c r="R2" t="n">
-        <v>6763486</v>
+        <v>6763206</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,72 +764,63 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130789515</v>
+        <v>130751852</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490723</v>
+        <v>490760</v>
       </c>
       <c r="R3" t="n">
-        <v>6763501</v>
+        <v>6763211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,26 +877,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130752197</v>
+        <v>130751938</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -933,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490715</v>
+        <v>490749</v>
       </c>
       <c r="R4" t="n">
-        <v>6763290</v>
+        <v>6763201</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130752899</v>
+        <v>130752001</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490652</v>
+        <v>490746</v>
       </c>
       <c r="R5" t="n">
-        <v>6763503</v>
+        <v>6763219</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,50 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130751615</v>
+        <v>130752039</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490779</v>
+        <v>490739</v>
       </c>
       <c r="R6" t="n">
-        <v>6763206</v>
+        <v>6763241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,40 +1210,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130752192</v>
+        <v>130752197</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Truppan, Dlr</t>
@@ -1336,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130789501</v>
+        <v>130752431</v>
       </c>
       <c r="B8" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1371,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490713</v>
+        <v>490682</v>
       </c>
       <c r="R8" t="n">
-        <v>6763507</v>
+        <v>6763392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,33 +1406,32 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130789509</v>
+        <v>130752527</v>
       </c>
       <c r="B9" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1479,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490693</v>
+        <v>490673</v>
       </c>
       <c r="R9" t="n">
-        <v>6763417</v>
+        <v>6763435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,33 +1513,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130752527</v>
+        <v>130752569</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1587,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490673</v>
+        <v>490661</v>
       </c>
       <c r="R10" t="n">
-        <v>6763435</v>
+        <v>6763445</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,53 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130789462</v>
+        <v>130752740</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490705</v>
+        <v>490682</v>
       </c>
       <c r="R11" t="n">
-        <v>6763439</v>
+        <v>6763461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,12 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ring hack på tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,26 +1733,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130751852</v>
+        <v>130752842</v>
       </c>
       <c r="B12" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1810,14 +1776,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490760</v>
+        <v>490660</v>
       </c>
       <c r="R12" t="n">
-        <v>6763211</v>
+        <v>6763462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130789504</v>
+        <v>130752874</v>
       </c>
       <c r="B13" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1921,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490686</v>
+        <v>490655</v>
       </c>
       <c r="R13" t="n">
-        <v>6763480</v>
+        <v>6763493</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,33 +1941,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130751762</v>
+        <v>130752899</v>
       </c>
       <c r="B14" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2025,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490779</v>
+        <v>490652</v>
       </c>
       <c r="R14" t="n">
-        <v>6763206</v>
+        <v>6763503</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,14 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130789505</v>
+        <v>130753055</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2136,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490697</v>
+        <v>490658</v>
       </c>
       <c r="R15" t="n">
-        <v>6763451</v>
+        <v>6763532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2181,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,33 +2155,32 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130789510</v>
+        <v>130753551</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2244,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490692</v>
+        <v>490770</v>
       </c>
       <c r="R16" t="n">
-        <v>6763414</v>
+        <v>6763512</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2289,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,33 +2262,32 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130753551</v>
+        <v>130789501</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2352,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490770</v>
+        <v>490713</v>
       </c>
       <c r="R17" t="n">
-        <v>6763512</v>
+        <v>6763507</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2397,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,32 +2369,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130789514</v>
+        <v>130789502</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2459,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490800</v>
+        <v>490712</v>
       </c>
       <c r="R18" t="n">
-        <v>6763195</v>
+        <v>6763506</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,7 +2458,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2504,7 +2468,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,14 +2496,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130752453</v>
+        <v>130789503</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2567,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490682</v>
+        <v>490685</v>
       </c>
       <c r="R19" t="n">
-        <v>6763392</v>
+        <v>6763486</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,7 +2566,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2612,7 +2576,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,32 +2585,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130789512</v>
+        <v>130789504</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2677,7 +2642,7 @@
         <v>490686</v>
       </c>
       <c r="R20" t="n">
-        <v>6763382</v>
+        <v>6763480</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,7 +2674,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2719,7 +2684,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2747,14 +2712,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130752039</v>
+        <v>130789505</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2778,14 +2743,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490739</v>
+        <v>490697</v>
       </c>
       <c r="R21" t="n">
-        <v>6763241</v>
+        <v>6763451</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,7 +2782,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2827,7 +2792,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,32 +2801,33 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130789502</v>
+        <v>130789506</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2889,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490712</v>
+        <v>490698</v>
       </c>
       <c r="R22" t="n">
-        <v>6763506</v>
+        <v>6763446</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2924,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2934,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,50 +2928,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130753344</v>
+        <v>130789507</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490761</v>
+        <v>490706</v>
       </c>
       <c r="R23" t="n">
-        <v>6763503</v>
+        <v>6763438</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +2998,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,12 +3008,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3 Bilder</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3061,32 +3017,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130752740</v>
+        <v>130789508</v>
       </c>
       <c r="B24" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3114,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490682</v>
+        <v>490700</v>
       </c>
       <c r="R24" t="n">
-        <v>6763461</v>
+        <v>6763430</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,7 +3106,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3159,7 +3116,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,32 +3125,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130752001</v>
+        <v>130789509</v>
       </c>
       <c r="B25" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3217,14 +3175,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490746</v>
+        <v>490693</v>
       </c>
       <c r="R25" t="n">
-        <v>6763219</v>
+        <v>6763417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,7 +3214,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3266,7 +3224,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3275,32 +3233,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130789507</v>
+        <v>130789510</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3328,10 +3287,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490706</v>
+        <v>490692</v>
       </c>
       <c r="R26" t="n">
-        <v>6763438</v>
+        <v>6763414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,7 +3322,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3373,7 +3332,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3401,14 +3360,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130752569</v>
+        <v>130789511</v>
       </c>
       <c r="B27" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3436,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490661</v>
+        <v>490679</v>
       </c>
       <c r="R27" t="n">
-        <v>6763445</v>
+        <v>6763384</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3481,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3490,32 +3449,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130751938</v>
+        <v>130789512</v>
       </c>
       <c r="B28" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3539,14 +3499,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490749</v>
+        <v>490686</v>
       </c>
       <c r="R28" t="n">
-        <v>6763201</v>
+        <v>6763382</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3538,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3548,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,71 +3557,64 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130789461</v>
+        <v>130789513</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490783</v>
+        <v>490777</v>
       </c>
       <c r="R29" t="n">
-        <v>6763515</v>
+        <v>6763210</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3693,7 +3646,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3703,12 +3656,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3717,6 +3665,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3735,14 +3684,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130789506</v>
+        <v>130789514</v>
       </c>
       <c r="B30" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3770,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490698</v>
+        <v>490800</v>
       </c>
       <c r="R30" t="n">
-        <v>6763446</v>
+        <v>6763195</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3754,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3764,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,54 +3792,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130789466</v>
+        <v>130807068</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490710</v>
+        <v>490844</v>
       </c>
       <c r="R31" t="n">
-        <v>6763505</v>
+        <v>6763171</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3917,22 +3857,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 bild, granar med lav och hackspår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3941,33 +3886,32 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130752874</v>
+        <v>130807229</v>
       </c>
       <c r="B32" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3991,14 +3935,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490655</v>
+        <v>490993</v>
       </c>
       <c r="R32" t="n">
-        <v>6763493</v>
+        <v>6763224</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4025,22 +3969,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 bilder på tall. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,21 +4009,21 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130752842</v>
+        <v>130807362</v>
       </c>
       <c r="B33" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4098,14 +4047,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490660</v>
+        <v>490990</v>
       </c>
       <c r="R33" t="n">
-        <v>6763462</v>
+        <v>6763195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4132,22 +4081,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4167,21 +4116,21 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130789513</v>
+        <v>130807544</v>
       </c>
       <c r="B34" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4205,17 +4154,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490777</v>
+        <v>491106</v>
       </c>
       <c r="R34" t="n">
-        <v>6763210</v>
+        <v>6763223</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4239,22 +4188,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2 bilder på gran vid basväg samt tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4263,33 +4217,32 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130753055</v>
+        <v>130811340</v>
       </c>
       <c r="B35" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4313,17 +4266,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490658</v>
+        <v>491007</v>
       </c>
       <c r="R35" t="n">
-        <v>6763532</v>
+        <v>6763275</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4347,22 +4300,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 bild på gran. Måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4382,21 +4340,21 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130789508</v>
+        <v>130813058</v>
       </c>
       <c r="B36" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4420,17 +4378,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490700</v>
+        <v>490951</v>
       </c>
       <c r="R36" t="n">
-        <v>6763430</v>
+        <v>6763295</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4454,22 +4412,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>3 bilder på tall och gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4478,69 +4441,63 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130753455</v>
+        <v>130815455</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490770</v>
+        <v>491031</v>
       </c>
       <c r="R37" t="n">
-        <v>6763512</v>
+        <v>6763301</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4567,27 +4524,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Bild 4 till 6</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4607,21 +4559,21 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130789511</v>
+        <v>130815610</v>
       </c>
       <c r="B38" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4649,13 +4601,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490679</v>
+        <v>490831</v>
       </c>
       <c r="R38" t="n">
-        <v>6763384</v>
+        <v>6763410</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4679,22 +4631,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter. 2 bilder på tall och gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4703,33 +4660,32 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130807229</v>
+        <v>130815712</v>
       </c>
       <c r="B39" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4753,14 +4709,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490993</v>
+        <v>490815</v>
       </c>
       <c r="R39" t="n">
-        <v>6763224</v>
+        <v>6763446</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4803,11 +4759,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 bilder på tall. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4834,53 +4785,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130807313</v>
+        <v>130815999</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490990</v>
+        <v>490722</v>
       </c>
       <c r="R40" t="n">
-        <v>6763195</v>
+        <v>6763404</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4924,7 +4870,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>2 bilder på tall</t>
+          <t>Måttligt i en radie av ca 50 meter. 2 bilder tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4951,14 +4897,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130812290</v>
+        <v>130751615</v>
       </c>
       <c r="B41" t="n">
-        <v>57881</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4982,7 +4928,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4991,13 +4937,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490970</v>
+        <v>490779</v>
       </c>
       <c r="R41" t="n">
-        <v>6763268</v>
+        <v>6763206</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5021,22 +4967,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5056,34 +5002,34 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130815695</v>
+        <v>130752192</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5099,14 +5045,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490815</v>
+        <v>490715</v>
       </c>
       <c r="R42" t="n">
-        <v>6763446</v>
+        <v>6763290</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5133,27 +5079,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>3 bilder på tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5173,55 +5114,63 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130815610</v>
+        <v>130789515</v>
       </c>
       <c r="B43" t="n">
-        <v>79244</v>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490831</v>
+        <v>490723</v>
       </c>
       <c r="R43" t="n">
-        <v>6763410</v>
+        <v>6763501</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5245,27 +5194,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter. 2 bilder på tall och gran</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,57 +5224,62 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130807544</v>
+        <v>130812290</v>
       </c>
       <c r="B44" t="n">
-        <v>79244</v>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491106</v>
+        <v>490970</v>
       </c>
       <c r="R44" t="n">
-        <v>6763223</v>
+        <v>6763268</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5373,11 +5322,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2 bilder på gran vid basväg samt tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5404,10 +5348,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130815959</v>
+        <v>130753344</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5444,10 +5388,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490727</v>
+        <v>490761</v>
       </c>
       <c r="R45" t="n">
-        <v>6763422</v>
+        <v>6763503</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5474,27 +5418,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>3 bilder på tall</t>
+          <t>3 Bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5514,17 +5458,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130807362</v>
+        <v>130753455</v>
       </c>
       <c r="B46" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5532,34 +5476,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490990</v>
+        <v>490770</v>
       </c>
       <c r="R46" t="n">
-        <v>6763195</v>
+        <v>6763512</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5586,22 +5535,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Bild 4 till 6</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5621,17 +5575,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130815712</v>
+        <v>130789461</v>
       </c>
       <c r="B47" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5639,34 +5593,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490815</v>
+        <v>490783</v>
       </c>
       <c r="R47" t="n">
-        <v>6763446</v>
+        <v>6763515</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5693,22 +5655,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5723,22 +5690,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130814260</v>
+        <v>130789462</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5764,21 +5731,24 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490982</v>
+        <v>490705</v>
       </c>
       <c r="R48" t="n">
-        <v>6763304</v>
+        <v>6763439</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5805,27 +5775,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4 bilder på tall</t>
+          <t>Äldre ring hack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5840,22 +5810,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130815999</v>
+        <v>130807313</v>
       </c>
       <c r="B49" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5863,37 +5833,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490722</v>
+        <v>490990</v>
       </c>
       <c r="R49" t="n">
-        <v>6763404</v>
+        <v>6763195</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5937,7 +5912,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Måttligt i en radie av ca 50 meter. 2 bilder tall</t>
+          <t>2 bilder på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5964,10 +5939,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130811340</v>
+        <v>130814260</v>
       </c>
       <c r="B50" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5975,37 +5950,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491007</v>
+        <v>490982</v>
       </c>
       <c r="R50" t="n">
-        <v>6763275</v>
+        <v>6763304</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6049,7 +6029,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 bild på gran. Måttligt i en radie av ca 50 meter</t>
+          <t>4 bilder på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6076,10 +6056,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130815884</v>
+        <v>130814854</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6105,21 +6085,24 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Truppan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490768</v>
+        <v>490993</v>
       </c>
       <c r="R51" t="n">
-        <v>6763431</v>
+        <v>6763309</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6166,14 +6149,14 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 bilder på tall, ett tydligt ringhack</t>
+          <t>2 bilder på högstubbe gran. Sannolikt bo där tretåig hackspett häckat. Platsen ligger i ett habitat område för fågeln, vidare stämmer höjd över mark, 3 meter, samt håldiametern, ca 4 cm.</t>
         </is>
       </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG51" t="b">
         <v>0</v>
@@ -6193,10 +6176,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130813058</v>
+        <v>130815695</v>
       </c>
       <c r="B52" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6204,37 +6187,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Truppan, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490951</v>
+        <v>490815</v>
       </c>
       <c r="R52" t="n">
-        <v>6763295</v>
+        <v>6763446</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6278,7 +6266,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>3 bilder på tall och gran</t>
+          <t>3 bilder på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6302,6 +6290,576 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130815884</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>490768</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6763431</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>3 bilder på tall, ett tydligt ringhack</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130815959</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>490727</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6763422</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>3 bilder på tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130789466</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>490710</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6763505</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130815454</v>
+      </c>
+      <c r="B56" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Truppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>491031</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6763301</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130752719</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>490682</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6763461</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61770-2025 artfynd.xlsx
+++ b/artfynd/A 61770-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130751762</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130751852</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130751938</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752039</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752197</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752431</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752527</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752569</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752740</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752842</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752874</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752899</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130753055</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130753551</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2385,6 +2465,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789501</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2493,6 +2578,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789502</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2601,6 +2691,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789503</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2709,6 +2804,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789504</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789505</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2925,6 +3030,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789506</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3033,6 +3143,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789507</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3141,6 +3256,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789508</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3249,6 +3369,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789509</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3357,6 +3482,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789510</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3465,6 +3595,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789511</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3573,6 +3708,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789512</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3681,6 +3821,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789513</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3789,6 +3934,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789514</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3901,6 +4051,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130807068</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4013,6 +4168,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130807229</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4120,6 +4280,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130807362</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4232,6 +4397,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130807544</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4344,6 +4514,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130811340</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4456,6 +4631,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130813058</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4563,6 +4743,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130815455</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4675,6 +4860,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130815610</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4782,6 +4972,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130815712</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4894,6 +5089,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130815999</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5006,6 +5206,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130751615</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5118,6 +5323,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752192</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5233,6 +5443,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789515</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5345,6 +5560,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130812290</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5462,6 +5682,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130753344</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5579,6 +5804,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130753455</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5699,6 +5929,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789461</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5819,6 +6054,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789462</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5936,6 +6176,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130807313</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6053,6 +6298,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130814260</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6173,6 +6423,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130814854</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6290,6 +6545,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130815695</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6407,6 +6667,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130815884</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6524,6 +6789,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130815959</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6641,6 +6911,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789466</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6753,6 +7028,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130815454</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6860,8 +7140,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130752719</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>